--- a/out/Attention-S4_repeat_2_000007.xlsx
+++ b/out/Attention-S4_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2554444171274073</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2554444171274073</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC39" t="n">
-        <v>-3.476542079274077e-05</v>
+        <v>-5.77114113640273e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.4007938808485579</v>
+        <v>0.6653272630790739</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC40" t="n">
-        <v>0.802207468261584</v>
+        <v>1.331683153591536</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.0601008529751682</v>
+        <v>0.09976881366469541</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.5210772213280059</v>
+        <v>0.8650004056209782</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.07514562177184836</v>
+        <v>0.1247434230127987</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.6112771563311231</v>
+        <v>1.014734395541674</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1077207297643025</v>
+        <v>0.1788191053054309</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.7516157276923314</v>
+        <v>1.2476997935614</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.115239843548806</v>
+        <v>0.1913013702867537</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.8743830878165404</v>
+        <v>1.451496435934952</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1221310064954788</v>
+        <v>0.2027401561802915</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.003414758000803</v>
+        <v>1.66569133039293</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.05511611760702081</v>
+        <v>0.09149352762836521</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.9914130196187706</v>
+        <v>1.645768276485645</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02661792247460233</v>
+        <v>0.04418654882931739</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.9894908156945051</v>
+        <v>1.642577390389271</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01268211198624224</v>
+        <v>0.02105418789541849</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.9882158400276494</v>
+        <v>1.640462839758584</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.00375374779046707</v>
+        <v>0.006235117151465533</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.9830311426205693</v>
+        <v>1.631859551337151</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002481748827999243</v>
+        <v>0.004122599330277831</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.9842385959765559</v>
+        <v>1.633867027066029</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001267253966843507</v>
+        <v>0.002107551637133032</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9842908606850826</v>
+        <v>1.633957076191057</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0006463104029367792</v>
+        <v>0.001075148473494844</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.2554444171274073</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.984314486156618</v>
+        <v>1.633999572079852</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002394738282501045</v>
+        <v>0.0004014472005272636</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.9841473873205466</v>
+        <v>1.63372549225492</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001286509683158936</v>
+        <v>0.0002161016019053054</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.9841643219328315</v>
+        <v>1.633756847347282</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>5.93731259952246e-05</v>
+        <v>0.000101493813374816</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.9841543327059064</v>
+        <v>1.633743563252066</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.435820469740162e-05</v>
+        <v>6.092499286814771e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.984164630441848</v>
+        <v>1.633764059079324</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.558738314970903e-05</v>
+        <v>2.999855135450535e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.984161469604619</v>
+        <v>1.633762108359411</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.990931307851776e-06</v>
+        <v>1.198458322334802e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.9841558208829714</v>
+        <v>1.633756057063693</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.395731888813558e-06</v>
+        <v>5.233171022101693e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.9841538974068871</v>
+        <v>1.633755811268129</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.503166167089948e-06</v>
+        <v>-3.375548894532629e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9841482111293017</v>
+        <v>1.633749782559842</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.970630842514548e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>3.828705708809411</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.9841428006593841</v>
+        <v>1.633744098025814</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>3.828705708809411</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.9841379660250656</v>
+        <v>1.6337393467506</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>3.828705708809411</v>
+        <v>0.04545455991735459</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.9841378220411581</v>
+        <v>1.633734057603038</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2554444171274073</v>
+        <v>0.04545455991735459</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.9841377993068567</v>
+        <v>1.633734034868737</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.9841381175870735</v>
+        <v>1.633734353148953</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.9841392088335303</v>
+        <v>1.633735444395411</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2554444171274073</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.9841385192263944</v>
+        <v>1.633734754788275</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.9841385495387961</v>
+        <v>1.633734785100676</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>3.228705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.984138360086286</v>
+        <v>1.633734595648166</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.9841384131329889</v>
+        <v>1.633734648694869</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.9841384661796917</v>
+        <v>1.633734701741572</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.9841384282891897</v>
+        <v>1.63373466385107</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.984138299461483</v>
+        <v>1.633734535023363</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.9841381554775754</v>
+        <v>1.633734391039456</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.9841380493841699</v>
+        <v>1.63373428494605</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8554444171274074</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.9841378144630576</v>
+        <v>1.633734050024938</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.04545455991735459</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.9841379811812663</v>
+        <v>1.633734216743147</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.04545455991735459</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.9841381782118767</v>
+        <v>1.633734413773757</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.9841380190717682</v>
+        <v>1.633734254633649</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.9841380569622703</v>
+        <v>1.63373429252415</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.9841382539928805</v>
+        <v>1.633734489554761</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.9841382312585792</v>
+        <v>1.63373446682046</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.9841380796965714</v>
+        <v>1.633734315258452</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.9841380039155674</v>
+        <v>1.633734239477448</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.9841381024308726</v>
+        <v>1.633734337992753</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.9841381100089729</v>
+        <v>1.633734345570854</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8554444171274074</v>
+        <v>7.999999562500022</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.9841383752424868</v>
+        <v>1.633734610804367</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.04545455991735459</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.9841380796965714</v>
+        <v>1.633734315258452</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.04545455991735459</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.9841383221957842</v>
+        <v>1.633734557757665</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.9841384055548885</v>
+        <v>1.633734641116769</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.9841382388366798</v>
+        <v>1.63373447439856</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.9841384282891897</v>
+        <v>1.63373466385107</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.9841380796965714</v>
+        <v>1.633734315258452</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.9841378750878608</v>
+        <v>1.633734110649741</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.9841379887593668</v>
+        <v>1.633734224321247</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.9841380039155674</v>
+        <v>1.633734239477448</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.9841377689944553</v>
+        <v>1.633734004556336</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.9841378296192584</v>
+        <v>1.633734065181139</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.9841377007915517</v>
+        <v>1.633733936353432</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.9841378371973587</v>
+        <v>1.633734072759239</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.984138011493668</v>
+        <v>1.633734247055548</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.9841381554775754</v>
+        <v>1.633734391039456</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.9841379887593668</v>
+        <v>1.633734224321247</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.9841379811812663</v>
+        <v>1.633734216743147</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.9841376932134512</v>
+        <v>1.633733928775331</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.9841377083696521</v>
+        <v>1.633733943931533</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.9841379357126639</v>
+        <v>1.633734171274544</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.9841379205564631</v>
+        <v>1.633734156118344</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.9841380266498686</v>
+        <v>1.633734262211749</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.9841377538382544</v>
+        <v>1.633733989400135</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.9841378523535596</v>
+        <v>1.63373408791544</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9841380039155674</v>
+        <v>1.633734239477448</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.9841380190717682</v>
+        <v>1.633734254633649</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.9841380796965714</v>
+        <v>1.633734315258452</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.9841381782118767</v>
+        <v>1.633734413773757</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.984138011493668</v>
+        <v>1.633734247055548</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.9841379660250656</v>
+        <v>1.633734201586946</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.9841379508688648</v>
+        <v>1.633734186430745</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.9841379887593668</v>
+        <v>1.633734224321247</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.9841380039155674</v>
+        <v>1.633734239477448</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.5545454400826454</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.633734231899347</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_2_000007.xlsx
+++ b/out/Attention-S4_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.5126438570410506</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2554444171274073</v>
+        <v>0.7126438570410507</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2554444171274073</v>
+        <v>-0.2208761717445079</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC39" t="n">
-        <v>-3.476542079274077e-05</v>
+        <v>-6.790477814991028e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.4007938808485579</v>
+        <v>0.7828418031422393</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC40" t="n">
-        <v>0.802207468261584</v>
+        <v>1.566893738433658</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.0601008529751682</v>
+        <v>0.1173905977724505</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.5210772213280059</v>
+        <v>1.017782494881275</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.07514562177184836</v>
+        <v>0.1467765003865462</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.6112771563311231</v>
+        <v>1.193963494954007</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1077207297643025</v>
+        <v>0.2104034172309953</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.7516157276923314</v>
+        <v>1.468076661505067</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.115239843548806</v>
+        <v>0.2250896317136195</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.8743830878165404</v>
+        <v>1.707868891654397</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1221310064954788</v>
+        <v>0.2385503784465531</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.003414758000803</v>
+        <v>1.959896353296894</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.05511611760702081</v>
+        <v>0.1076526831855109</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.9914130196187706</v>
+        <v>1.93645443954015</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02661792247460233</v>
+        <v>0.05199196870927134</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.7126438570410507</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.9894908156945051</v>
+        <v>1.932699946589904</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01268211198624224</v>
+        <v>0.02477201229497627</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.9882158400276494</v>
+        <v>1.930211940361028</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.00375374779046707</v>
+        <v>0.007337382838327806</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.9830311426205693</v>
+        <v>1.920089834574048</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002481748827999243</v>
+        <v>0.004851225388114485</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.9842385959765559</v>
+        <v>1.922452798275387</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001267253966843507</v>
+        <v>0.002480470626640912</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9842908606850826</v>
+        <v>1.922559648718035</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0006463104029367792</v>
+        <v>0.001266414279612291</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.2554444171274073</v>
+        <v>0.7126438570410507</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.984314486156618</v>
+        <v>1.922610550850403</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002394738282501045</v>
+        <v>0.0004733512676596473</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.9841473873205466</v>
+        <v>1.922288868449365</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001286509683158936</v>
+        <v>0.0002557018888137184</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.9841643219328315</v>
+        <v>1.922326654483205</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>5.93731259952246e-05</v>
+        <v>0.0001205673321882159</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.9841543327059064</v>
+        <v>1.922311922410932</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.435820469740162e-05</v>
+        <v>7.273245427736819e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.984164630441848</v>
+        <v>1.922336761270708</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.558738314970903e-05</v>
+        <v>3.514539714193261e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.984161469604619</v>
+        <v>1.92233530444294</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.990931307851776e-06</v>
+        <v>1.498186261570356e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.9841558208829714</v>
+        <v>1.922329067624448</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.395731888813558e-06</v>
+        <v>7.791463777627117e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.9841538974068871</v>
+        <v>1.92232965989285</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.503166167089948e-06</v>
+        <v>8.280563881834207e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.5126438570410506</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9841482111293017</v>
+        <v>1.922323516096875</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.970630842514548e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.9841428006593841</v>
+        <v>1.922317831562846</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.9841379660250656</v>
+        <v>1.922313080287632</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.9841378220411581</v>
+        <v>1.922307791140071</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2554444171274073</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.9841377993068567</v>
+        <v>1.922307768405769</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.9841381175870735</v>
+        <v>1.922308086685986</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.9841392088335303</v>
+        <v>1.922309177932443</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2554444171274073</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.9841385192263944</v>
+        <v>1.922308488325307</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.9841385495387961</v>
+        <v>1.922308518637708</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>3.228705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.984138360086286</v>
+        <v>1.922308329185199</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.9841384131329889</v>
+        <v>1.922308382231901</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.9841384661796917</v>
+        <v>1.922308435278604</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.9841384282891897</v>
+        <v>1.922308397388102</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.5126438570410506</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.984138299461483</v>
+        <v>1.922308268560396</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.9841381554775754</v>
+        <v>1.922308124576488</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.922307965436379</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.9841380493841699</v>
+        <v>1.922308018483082</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.922307965436379</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.922307965436379</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.9841378144630576</v>
+        <v>1.92230778356197</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.9841379811812663</v>
+        <v>1.922307950280179</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.9841381782118767</v>
+        <v>1.922308147310789</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.9841380190717682</v>
+        <v>1.922307988170681</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.9841380569622703</v>
+        <v>1.922308026061183</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.9841382539928805</v>
+        <v>1.922308223091793</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.9841382312585792</v>
+        <v>1.922308200357492</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.9841380796965714</v>
+        <v>1.922308048795484</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.9841380039155674</v>
+        <v>1.92230797301448</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.9841381024308726</v>
+        <v>1.922308071529785</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.9841381100089729</v>
+        <v>1.922308079107886</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.9841383752424868</v>
+        <v>1.9223083443414</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.9841380796965714</v>
+        <v>1.922308048795484</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.9841383221957842</v>
+        <v>1.922308291294697</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.9841384055548885</v>
+        <v>1.922308374653801</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.9841382388366798</v>
+        <v>1.922308207935592</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.9841384282891897</v>
+        <v>1.922308397388102</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.9841380796965714</v>
+        <v>1.922308048795484</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.9841378750878608</v>
+        <v>1.922307844186774</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.9841379887593668</v>
+        <v>1.922307957858279</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.9841380039155674</v>
+        <v>1.92230797301448</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.9841377689944553</v>
+        <v>1.922307738093368</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.9841378296192584</v>
+        <v>1.922307798718171</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.9841377007915517</v>
+        <v>1.922307669890464</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.9841378371973587</v>
+        <v>1.922307806296271</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.984138011493668</v>
+        <v>1.92230798059258</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.9841381554775754</v>
+        <v>1.922308124576488</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.9841379887593668</v>
+        <v>1.922307957858279</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.9841379811812663</v>
+        <v>1.922307950280179</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.9841376932134512</v>
+        <v>1.922307662312364</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.9841377083696521</v>
+        <v>1.922307677468565</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.9841379357126639</v>
+        <v>1.922307904811577</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.9841379205564631</v>
+        <v>1.922307889655376</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.9841380266498686</v>
+        <v>1.922307995748781</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.9841377538382544</v>
+        <v>1.922307722937167</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.9841378523535596</v>
+        <v>1.922307821452472</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9841380039155674</v>
+        <v>1.92230797301448</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.9841380190717682</v>
+        <v>1.922307988170681</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.922307965436379</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.9841380796965714</v>
+        <v>1.922308048795484</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.9841381782118767</v>
+        <v>1.922308147310789</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.984138011493668</v>
+        <v>1.92230798059258</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.922307965436379</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.9841379660250656</v>
+        <v>1.922307935123978</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.9841379508688648</v>
+        <v>1.922307919967777</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.9841379887593668</v>
+        <v>1.922307957858279</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.9841380039155674</v>
+        <v>1.92230797301448</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.9841379963374671</v>
+        <v>1.922307965436379</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_2_000007.xlsx
+++ b/out/Attention-S4_repeat_2_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.0001906752586364746</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.4399999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.0008410587906837463</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.2299999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.001416571438312531</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5126438570410506</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>5.640462040901184e-05</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.646163885826609</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.002237558364868164</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.579683914612168</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0002709180116653442</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.646163885826609</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.00214371457695961</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7126438570410507</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001138713210821152</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2208761717445079</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001857534050941467</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.002167932689189911</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.001762915402650833</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001854341477155685</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0017438605427742</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.002177227288484573</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0004068613052368164</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.001581903547048569</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.002165630459785461</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.00258307158946991</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.001103837043046951</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.002292133867740631</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.002310566604137421</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001653879880905151</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.001871127635240555</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.002966668456792831</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.00289490818977356</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.002086181193590164</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.002680592238903046</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.002397172152996063</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.003226965665817261</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.002996034920215607</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.00443616509437561</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.002800054848194122</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.002974133938550949</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.003098390996456146</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.001665536314249039</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.004346616566181183</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.001969359815120697</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.003810800611972809</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-6.790477814991028e-05</v>
+        <v>-9.084902306029107e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.7828418031422393</v>
+        <v>1.047355060480815</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.005932576954364777</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.566893738433658</v>
+        <v>2.096329142870279</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1173905977724505</v>
+        <v>0.1570555633350144</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.007123637944459915</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.017782494881275</v>
+        <v>1.361679514504647</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1467765003865462</v>
+        <v>0.1963705567442412</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.003952208906412125</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.193963494954007</v>
+        <v>1.597390006176859</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2104034172309953</v>
+        <v>0.281496261824816</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.005343377590179443</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.468076661505067</v>
+        <v>1.964122793678942</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2250896317136195</v>
+        <v>0.3011448933736316</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.007626753300428391</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.707868891654397</v>
+        <v>2.284938003109176</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2385503784465531</v>
+        <v>0.3191536261581864</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.008209221065044403</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.959896353296894</v>
+        <v>2.622122453615792</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1076526831855109</v>
+        <v>0.1440274297561289</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.009880781173706055</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.93645443954015</v>
+        <v>2.590759804310038</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.05199196870927134</v>
+        <v>0.06955930873902265</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.006862111389636993</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7126438570410507</v>
+        <v>0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.932699946589904</v>
+        <v>2.585736722076992</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02477201229497627</v>
+        <v>0.03314293970169569</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0001067966222763062</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.646163885826609</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.930211940361028</v>
+        <v>2.582408053006632</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.007337382838327806</v>
+        <v>0.009818025590435788</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.000918906182050705</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.579683914612168</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.920089834574048</v>
+        <v>2.568867857248673</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004851225388114485</v>
+        <v>0.006492075890393073</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.001354899257421494</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.579683914612168</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.922452798275387</v>
+        <v>2.572030843322902</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002480470626640912</v>
+        <v>0.003320768296930436</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.0007746517658233643</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.646163885826609</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.922559648718035</v>
+        <v>2.572175478182052</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001266414279612291</v>
+        <v>0.001696259012307816</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.001492161303758621</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7126438570410507</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.922610550850403</v>
+        <v>2.572245249506464</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004733512676596473</v>
+        <v>0.0006345677550196233</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.006190810352563858</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.16</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.922288868449365</v>
+        <v>2.571816837119001</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002557018888137184</v>
+        <v>0.0003431525224031302</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.007601872086524963</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.922326654483205</v>
+        <v>2.571869043632918</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001205673321882159</v>
+        <v>0.0001626880195678073</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.01038680225610733</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.922311922410932</v>
+        <v>2.571851016692353</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.273245427736819e-05</v>
+        <v>9.929924244811426e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01356106624007225</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.922336761270708</v>
+        <v>2.571886053643447</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.514539714193261e-05</v>
+        <v>4.955656534672894e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01085783541202545</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.92233530444294</v>
+        <v>2.571885806932994</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.498186261570356e-05</v>
+        <v>2.097642140041462e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.008146751672029495</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.922329067624448</v>
+        <v>2.571879168756554</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>7.791463777627117e-06</v>
+        <v>1.162890291091525e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.009621620178222656</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.92232965989285</v>
+        <v>2.57188171909519</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.280563881834207e-07</v>
+        <v>3.15927894345679e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.002441469579935074</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5126438570410506</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.922323516096875</v>
+        <v>2.571875117780825</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>-1.911892527543644e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0009035244584083557</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.646163885826609</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.922317831562846</v>
+        <v>2.571869159182686</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.0048476941883564</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.579683914612168</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.922313080287632</v>
+        <v>2.571864489914049</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.001450832933187485</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.646163885826609</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.922307791140071</v>
+        <v>2.571859200766487</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.002522166818380356</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.646163885826609</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.922307768405769</v>
+        <v>2.571859178032186</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.002774488180875778</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.646163885826609</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.922308086685986</v>
+        <v>2.571859496312402</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.003416795283555984</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.646163885826609</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.922309177932443</v>
+        <v>2.571860587558859</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.005742892622947693</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.646163885826609</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.922308488325307</v>
+        <v>2.571859897951724</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0003772750496864319</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.646163885826609</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.922308518637708</v>
+        <v>2.571859928264125</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.009088244289159775</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.579683914612168</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.922308329185199</v>
+        <v>2.571859738811615</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01033880189061165</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.579683914612168</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.922308382231901</v>
+        <v>2.571859791858318</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.006608616560697556</v>
       </c>
       <c r="JB71" t="n">
-        <v>2.579683914612168</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.922308435278604</v>
+        <v>2.571859844905021</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.003018628805875778</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.646163885826609</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.922308397388102</v>
+        <v>2.571859807014518</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.001315370202064514</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5126438570410506</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.922308268560396</v>
+        <v>2.571859678186812</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.003605399280786514</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.922308124576488</v>
+        <v>2.571859534202904</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.004410453140735626</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.922307965436379</v>
+        <v>2.571859375062796</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01393282786011696</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.922308018483082</v>
+        <v>2.571859428109499</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.01670539751648903</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.922307965436379</v>
+        <v>2.571859375062796</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01551733165979385</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.922307965436379</v>
+        <v>2.571859375062796</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01681134104728699</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.92230778356197</v>
+        <v>2.571859193188387</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.01498995721340179</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.922307950280179</v>
+        <v>2.571859359906595</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.008193656802177429</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.922308147310789</v>
+        <v>2.571859556937206</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.001307025551795959</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.922307988170681</v>
+        <v>2.571859397797097</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001376919448375702</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.922308026061183</v>
+        <v>2.571859435687599</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.005245227366685867</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.922308223091793</v>
+        <v>2.57185963271821</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.0196697786450386</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.922308200357492</v>
+        <v>2.571859609983909</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.02296483516693115</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.922308048795484</v>
+        <v>2.5718594584219</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.0237981416285038</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.92230797301448</v>
+        <v>2.571859382640896</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.02012443169951439</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.922308071529785</v>
+        <v>2.571859481156201</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01438411325216293</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.922308079107886</v>
+        <v>2.571859488734302</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01181645318865776</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.9223083443414</v>
+        <v>2.571859753967816</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.006740543991327286</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.922308048795484</v>
+        <v>2.5718594584219</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.005835969001054764</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.922308291294697</v>
+        <v>2.571859700921113</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.005582563579082489</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.922308374653801</v>
+        <v>2.571859784280217</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.002854641526937485</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.922308207935592</v>
+        <v>2.571859617562009</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.002136189490556717</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.922308397388102</v>
+        <v>2.571859807014518</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.002750292420387268</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.922308048795484</v>
+        <v>2.5718594584219</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01018457114696503</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.922307844186774</v>
+        <v>2.57185925381319</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01740849763154984</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.922307957858279</v>
+        <v>2.571859367484696</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.02034945413470268</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.92230797301448</v>
+        <v>2.571859382640896</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.02046094089746475</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.922307738093368</v>
+        <v>2.571859147719784</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01403544470667839</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.922307798718171</v>
+        <v>2.571859208344587</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.009467568248510361</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.922307669890464</v>
+        <v>2.571859079516881</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.007215999066829681</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.922307806296271</v>
+        <v>2.571859215922688</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.008352864533662796</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.92230798059258</v>
+        <v>2.571859390218997</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.009697441011667252</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.922308124576488</v>
+        <v>2.571859534202904</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.009918056428432465</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.922307957858279</v>
+        <v>2.571859367484696</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.0119854174554348</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.16</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.922307950280179</v>
+        <v>2.571859359906595</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01580699160695076</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.922307662312364</v>
+        <v>2.57185907193878</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01816152408719063</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.922307677468565</v>
+        <v>2.571859087094981</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01948554068803787</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.922307904811577</v>
+        <v>2.571859314437993</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01736196503043175</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.922307889655376</v>
+        <v>2.571859299281792</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01618033275008202</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.922307995748781</v>
+        <v>2.571859405375198</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01457194983959198</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.922307722937167</v>
+        <v>2.571859132563584</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01188536733388901</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.922307821452472</v>
+        <v>2.571859231078889</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.008976001292467117</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.92230797301448</v>
+        <v>2.571859382640896</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.006154295057058334</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.922307988170681</v>
+        <v>2.571859397797097</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.006687987595796585</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.922307965436379</v>
+        <v>2.571859375062796</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.005120657384395599</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.922308048795484</v>
+        <v>2.5718594584219</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.001754134893417358</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.922308147310789</v>
+        <v>2.571859556937206</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.0005205199122428894</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.92230798059258</v>
+        <v>2.571859390218997</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.000443633645772934</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.922307965436379</v>
+        <v>2.571859375062796</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.0006924867630004883</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.922307935123978</v>
+        <v>2.571859344750395</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.002130091190338135</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.922307919967777</v>
+        <v>2.571859329594194</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003637414425611496</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.922307957858279</v>
+        <v>2.571859367484696</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.005003418773412704</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.2300000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.92230797301448</v>
+        <v>2.571859382640896</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.005042873322963715</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.4400000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.922307965436379</v>
+        <v>2.571859375062796</v>
       </c>
     </row>
   </sheetData>
